--- a/docs/brand/XLOOP_招商手册_v0.1.xlsx
+++ b/docs/brand/XLOOP_招商手册_v0.1.xlsx
@@ -8,11 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="给商户看的一页" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="五带配额" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="优先P0" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="禁入" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合同条款清单" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待铺位表字段" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客群诚实版" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="五带配额" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="优先P0" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="禁入" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合同条款清单" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待铺位表字段" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -509,7 +510,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>康定路×同文路，商贸学院南门步行约6分钟，总部经济园贴着</t>
+          <t>康定路×同文路。商贸南门约6分钟；同文路对过农发行金科（云谷三期）；康定路北浙商科研（更近吾悦）</t>
         </is>
       </c>
     </row>
@@ -569,7 +570,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>15万师生、创新港下课就来、西工大2027年校门口</t>
+          <t>15万师生、创新港下课就来、西工大2027年校门口、农发行+浙商6000人天天来吃饭</t>
         </is>
       </c>
     </row>
@@ -594,6 +595,136 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>钱包</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>人从哪来</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>客单带</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>商户能指望什么</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A 南门学生</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>商贸约2万是校门口；服装来抢</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>日常15–35；夜聚40–80；玩一次80–150</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>晚上和周末的人头。没学生价，这层会走</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B 园区白领</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>总部约2万 + 云谷（含农发行金科，过马路）+ 浙商2027爬坡约0.2万</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>园区午餐28–48；银行金科可40–60；晚餐70–140</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>工作日中午翻台。农发行是保底，浙商是和吾悦抢的午饭</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C 目的地</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>创新港月约0.2–0.4万UV；周末年轻居民</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>一次120–280</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>高峰和内容，不是每天的保底</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>D 以后</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>西工大沣西1.8万，约2030年</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>略高于A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2027年工地，禁止当承诺客流</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -817,7 +948,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -917,7 +1048,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>可翻台简餐（园区午餐）</t>
+          <t>可翻台简餐（园区/农发行/浙商午餐）</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -932,7 +1063,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>28–48</t>
+          <t>28–48（园区）；银行金科可40–60</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -1162,13 +1293,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1271,12 +1402,24 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>物料写农发行+浙商规划6000人日均来吃饭</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>规划≠在岗；浙商更近吾悦</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1332,7 +1475,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>工卡午餐：11:00–14:00园区工卡套餐</t>
+          <t>工卡午餐：总部经济园/农发行金科/浙商科研 11:00–14:00套餐</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -1434,7 +1577,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>物料不得写15万师生/吾悦同级/西工大校门口</t>
+          <t>物料不得写15万师生/吾悦同级/西工大校门口/农发行浙商6000人日均来吃饭</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -1448,7 +1591,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
